--- a/Filtered_V3.0/COCHRA_HCA_Florida_Highlands_Hospital.xlsx
+++ b/Filtered_V3.0/COCHRA_HCA_Florida_Highlands_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -1875,7 +1890,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1920,22 +1935,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Candescent Health/Envision Healthcare (Candescent Health)-</t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2373,6 +2373,21 @@
       <c r="P25" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2394,7 +2409,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2439,7 +2454,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2476,7 +2491,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-radord</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2521,22 +2536,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3164,7 +3164,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3186,7 +3201,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3231,22 +3246,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3703,22 +3703,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4217,7 +4217,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4239,7 +4254,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4285,6 +4300,21 @@
       <c r="P51" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4306,7 +4336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4352,21 +4382,6 @@
       <c r="P52" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4388,7 +4403,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-riurl</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4433,22 +4448,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Charges </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4937,17 +4937,17 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-Patient Accounting</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5096,22 +5096,22 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5548,22 +5548,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5630,22 +5630,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5919,6 +5919,21 @@
       <c r="P73" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -5940,7 +5955,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5990,17 +6005,17 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6037,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6072,17 +6087,17 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6119,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6154,7 +6169,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6164,7 +6179,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6186,7 +6201,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6236,7 +6251,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6246,7 +6261,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6268,7 +6283,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6318,17 +6333,17 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -6350,7 +6365,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6432,7 +6447,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6514,7 +6529,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6564,17 +6579,17 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6611,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6646,17 +6661,17 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6693,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6728,17 +6743,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6775,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6806,21 +6821,6 @@
       <c r="P84" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6950,6 +6950,21 @@
       <c r="P86" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6971,7 +6986,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7017,6 +7032,21 @@
       <c r="P87" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7068,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7088,17 +7118,17 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7120,7 +7150,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7170,17 +7200,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7232,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7284,7 +7314,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7334,7 +7364,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -7344,7 +7374,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -7366,7 +7396,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7416,7 +7446,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -7426,7 +7456,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -7448,7 +7478,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7530,7 +7560,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7580,17 +7610,17 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -7612,7 +7642,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7662,17 +7692,17 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7724,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7776,7 +7806,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7826,17 +7856,17 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7888,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7940,7 +7970,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7990,17 +8020,17 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8052,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8072,17 +8102,17 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8134,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8154,17 +8184,17 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8216,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8236,17 +8266,17 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8298,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8318,17 +8348,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8380,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8396,21 +8426,6 @@
       <c r="P104" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8447,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8478,21 +8493,6 @@
       <c r="P105" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9038,7 +9038,22 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9060,7 +9075,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9127,7 +9142,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9172,22 +9187,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9317,6 +9317,21 @@
       <c r="P117" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9338,7 +9353,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9388,17 +9403,17 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9435,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9470,17 +9485,17 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -9502,7 +9517,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9552,17 +9567,17 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9599,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9634,7 +9649,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -9644,7 +9659,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -9666,7 +9681,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9716,7 +9731,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -9726,7 +9741,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -9748,7 +9763,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9798,17 +9813,17 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -9830,7 +9845,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9880,17 +9895,17 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9927,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9994,7 +10009,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10076,7 +10091,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10126,17 +10141,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -10158,7 +10173,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10208,17 +10223,17 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10255,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10290,17 +10305,17 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10337,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople EDM</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10372,17 +10387,17 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10419,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Meds</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10454,17 +10469,17 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10501,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople PCS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10536,17 +10551,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10583,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10614,21 +10629,6 @@
       <c r="P133" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -11242,6 +11242,21 @@
       <c r="P142" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -11263,7 +11278,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11313,17 +11328,17 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11360,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11395,17 +11410,17 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -11427,7 +11442,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11477,17 +11492,17 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11524,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11591,7 +11606,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11641,7 +11656,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -11651,7 +11666,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -11673,7 +11688,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11723,17 +11738,17 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -11755,7 +11770,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11805,17 +11820,17 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -11837,7 +11852,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11887,17 +11902,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11934,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11974,12 +11989,12 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12016,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -12051,17 +12066,17 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12083,7 +12098,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12165,7 +12180,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12215,17 +12230,17 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12262,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12297,17 +12312,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12344,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12379,17 +12394,17 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12426,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12461,17 +12476,17 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12508,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12539,21 +12554,6 @@
       <c r="P158" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom (Navacare Patient Flow)-Admissions </t>
+          <t>Hill-Rom (Navacare Patient Flow)-ADMO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -15400,6 +15400,21 @@
       <c r="P196" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -15421,7 +15436,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15471,17 +15486,17 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -15503,7 +15518,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15553,7 +15568,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -15563,7 +15578,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -15585,7 +15600,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15635,7 +15650,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -15645,7 +15660,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -15667,7 +15682,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15749,7 +15764,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15799,7 +15814,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -15809,7 +15824,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15846,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15881,17 +15896,17 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -15913,7 +15928,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15963,17 +15978,17 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -15995,7 +16010,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -16045,17 +16060,17 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -16077,7 +16092,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -16127,17 +16142,17 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16174,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16205,21 +16220,6 @@
       <c r="P206" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">LabCorp (LabCorp)-Ref Lab Orders </t>
+          <t>LabCorp (LabCorp)-LABRR</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -16348,22 +16348,22 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>LABSO</t>
+          <t>LABRR</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ref Lab Orders </t>
+          <t>Ref Lab Results</t>
         </is>
       </c>
     </row>
@@ -16385,7 +16385,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>LabCorp (LabCorp)-Ref Lab Results</t>
+          <t>LabCorp (LabCorp)-LABSO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16430,22 +16430,22 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>LABRR</t>
+          <t>LABSO</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>Ref Lab Results</t>
+          <t xml:space="preserve">Ref Lab Orders </t>
         </is>
       </c>
     </row>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17905,7 +17905,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (Wound Care)-Admissions </t>
+          <t>Net Health (Wound Care)-ADMO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (Wound Care)-Charges </t>
+          <t>Net Health (Wound Care)-Patient Accounting</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18794,7 +18794,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19128,6 +19128,21 @@
       <c r="P245" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19149,7 +19164,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-PHAORD</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -19195,6 +19210,21 @@
       <c r="P246" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>PHAORD</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>RDE</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -19216,7 +19246,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19262,21 +19292,6 @@
       <c r="P247" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19298,7 +19313,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-Pharmacy Orders </t>
+          <t>Patient Keeper (Portal)-oeordhq</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19344,21 +19359,6 @@
       <c r="P248" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Admissions </t>
+          <t>Provation (Apex)-ADMO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-ITS HM Results </t>
+          <t>Provation (Apex)-CWSO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19698,22 +19698,22 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Scheduling </t>
+          <t>Provation (Apex)-ITSHMRO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19780,22 +19780,22 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE to MD - CMORE)-ITS HM Results </t>
+          <t>Provation (MD - CMORE to MD - CMORE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20023,7 +20023,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -20152,7 +20152,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-Admissions </t>
+          <t>Provation (MD - CMORE)-ADMO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-ITS HM Results </t>
+          <t>Provation (MD - CMORE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -20768,7 +20768,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople ED Patient Visit Data</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Medication Administration</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -21841,7 +21841,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22016,6 +22016,21 @@
       <c r="P284" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -22037,7 +22052,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22087,17 +22102,17 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -22119,7 +22134,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22201,7 +22216,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22283,7 +22298,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22365,7 +22380,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22415,17 +22430,17 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -22447,7 +22462,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22497,17 +22512,17 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -22529,7 +22544,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -22579,17 +22594,17 @@
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22626,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22661,17 +22676,17 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22693,7 +22708,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22739,21 +22754,6 @@
       <c r="P293" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R293" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S293" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22837,7 +22837,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23063,7 +23063,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -23145,7 +23145,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
